--- a/pipeline_output/Maharashtra_2W_H&M.xlsx
+++ b/pipeline_output/Maharashtra_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7952,12 +7952,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8460,12 +8460,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9192,12 +9192,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10753,12 +10753,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11338,12 +11338,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11582,12 +11582,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12314,12 +12314,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12431,12 +12431,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12548,12 +12548,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12899,12 +12899,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -13016,12 +13016,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13143,12 +13143,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -14032,12 +14032,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14149,12 +14149,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14266,12 +14266,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14393,12 +14393,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14647,12 +14647,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15125,12 +15125,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15242,12 +15242,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15476,12 +15476,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15603,12 +15603,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15847,12 +15847,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15974,12 +15974,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16218,12 +16218,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16335,12 +16335,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16452,12 +16452,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16569,12 +16569,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17067,12 +17067,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17194,12 +17194,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17438,12 +17438,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17565,12 +17565,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17682,12 +17682,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17809,12 +17809,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17936,12 +17936,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -18053,12 +18053,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18170,12 +18170,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18287,12 +18287,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18404,12 +18404,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18521,12 +18521,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18638,12 +18638,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18755,12 +18755,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18882,12 +18882,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -19009,12 +19009,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19380,12 +19380,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19497,12 +19497,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19731,12 +19731,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19848,12 +19848,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19965,12 +19965,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20082,12 +20082,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20199,12 +20199,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20433,12 +20433,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20560,12 +20560,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20687,12 +20687,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20814,12 +20814,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20941,12 +20941,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21068,12 +21068,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21195,12 +21195,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21322,12 +21322,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21449,12 +21449,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21566,12 +21566,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21683,12 +21683,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21810,12 +21810,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21937,12 +21937,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22064,12 +22064,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22191,12 +22191,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22308,12 +22308,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22425,12 +22425,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22552,12 +22552,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22679,12 +22679,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22806,12 +22806,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22933,12 +22933,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -23050,12 +23050,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23167,12 +23167,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23284,12 +23284,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23411,12 +23411,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23538,12 +23538,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -23665,12 +23665,12 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -23792,12 +23792,12 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -23909,12 +23909,12 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -24026,12 +24026,12 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -24143,12 +24143,12 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -24260,12 +24260,12 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -24377,12 +24377,12 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -24504,12 +24504,12 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -24631,12 +24631,12 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -24758,12 +24758,12 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -24885,12 +24885,12 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -25129,12 +25129,12 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -25256,12 +25256,12 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -25500,12 +25500,12 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -25627,12 +25627,12 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -25744,12 +25744,12 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -25871,12 +25871,12 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -25998,12 +25998,12 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -26115,12 +26115,12 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -26242,12 +26242,12 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -26369,12 +26369,12 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -26496,12 +26496,12 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -26623,12 +26623,12 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -26740,12 +26740,12 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -26857,12 +26857,12 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -26974,12 +26974,12 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -27091,12 +27091,12 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -27208,12 +27208,12 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -27462,12 +27462,12 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -27589,12 +27589,12 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -27716,12 +27716,12 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -27833,12 +27833,12 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -27960,12 +27960,12 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -28087,12 +28087,12 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -28204,12 +28204,12 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -28331,12 +28331,12 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -28458,12 +28458,12 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -28575,12 +28575,12 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -28702,12 +28702,12 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -28829,12 +28829,12 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -28946,12 +28946,12 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -29073,12 +29073,12 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -29200,12 +29200,12 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -29327,12 +29327,12 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -29571,12 +29571,12 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
@@ -29805,12 +29805,12 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -29922,12 +29922,12 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -30039,12 +30039,12 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -30166,12 +30166,12 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN242" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -30293,12 +30293,12 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -30420,12 +30420,12 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -30547,12 +30547,12 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN245" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
@@ -30664,12 +30664,12 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
@@ -30791,12 +30791,12 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
@@ -30918,12 +30918,12 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -31035,12 +31035,12 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
@@ -31162,12 +31162,12 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -31289,12 +31289,12 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
@@ -31406,12 +31406,12 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
@@ -31533,12 +31533,12 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
@@ -31660,12 +31660,12 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
@@ -31777,12 +31777,12 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
@@ -31904,12 +31904,12 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN256" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -32031,12 +32031,12 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
@@ -32158,12 +32158,12 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
@@ -32285,12 +32285,12 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
@@ -32402,12 +32402,12 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
@@ -32519,12 +32519,12 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
@@ -32636,12 +32636,12 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN262" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
@@ -32753,12 +32753,12 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN263" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO263" t="inlineStr">
@@ -32870,12 +32870,12 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN264" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
@@ -32997,12 +32997,12 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN265" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO265" t="inlineStr">
@@ -33124,12 +33124,12 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN266" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
@@ -33251,12 +33251,12 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN267" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO267" t="inlineStr">
@@ -33378,12 +33378,12 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -33495,12 +33495,12 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN269" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO269" t="inlineStr">
@@ -33622,12 +33622,12 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN270" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
@@ -33749,12 +33749,12 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN271" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO271" t="inlineStr">
@@ -33866,12 +33866,12 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN272" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
@@ -33993,12 +33993,12 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN273" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO273" t="inlineStr">
@@ -34120,12 +34120,12 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN274" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
@@ -34237,12 +34237,12 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN275" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO275" t="inlineStr">
@@ -34364,12 +34364,12 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
@@ -34491,12 +34491,12 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
@@ -34618,12 +34618,12 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -34745,12 +34745,12 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
@@ -34872,12 +34872,12 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN280" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO280" t="inlineStr">
@@ -34999,12 +34999,12 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
@@ -35126,12 +35126,12 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
@@ -35253,12 +35253,12 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN283" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO283" t="inlineStr">
@@ -35380,12 +35380,12 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN284" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO284" t="inlineStr">
@@ -35507,12 +35507,12 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN285" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO285" t="inlineStr">
@@ -35624,12 +35624,12 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
@@ -35741,12 +35741,12 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
@@ -35858,12 +35858,12 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN288" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -35975,12 +35975,12 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN289" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
@@ -36092,12 +36092,12 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN290" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
@@ -36209,12 +36209,12 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN291" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO291" t="inlineStr">
@@ -36326,12 +36326,12 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN292" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO292" t="inlineStr">
@@ -36443,12 +36443,12 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN293" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
@@ -36560,12 +36560,12 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN294" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -36677,12 +36677,12 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
@@ -36794,12 +36794,12 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
@@ -36911,12 +36911,12 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN297" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO297" t="inlineStr">
@@ -37028,12 +37028,12 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN298" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
@@ -37145,12 +37145,12 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN299" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO299" t="inlineStr">
@@ -37262,12 +37262,12 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN300" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -37379,12 +37379,12 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN301" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
@@ -37506,12 +37506,12 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN302" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO302" t="inlineStr">
@@ -37633,12 +37633,12 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN303" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO303" t="inlineStr">
@@ -37760,12 +37760,12 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN304" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO304" t="inlineStr">
@@ -37887,12 +37887,12 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN305" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO305" t="inlineStr">
@@ -38014,12 +38014,12 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN306" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
@@ -38141,12 +38141,12 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN307" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO307" t="inlineStr">
@@ -38268,12 +38268,12 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN308" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO308" t="inlineStr">
@@ -38395,12 +38395,12 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN309" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO309" t="inlineStr">
@@ -38512,12 +38512,12 @@
       </c>
       <c r="AM310" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN310" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
@@ -38629,12 +38629,12 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN311" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO311" t="inlineStr">
@@ -38746,12 +38746,12 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN312" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -38863,12 +38863,12 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN313" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO313" t="inlineStr">
@@ -38980,12 +38980,12 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN314" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
@@ -39097,12 +39097,12 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN315" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO315" t="inlineStr">
@@ -39214,12 +39214,12 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN316" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO316" t="inlineStr">
@@ -39331,12 +39331,12 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN317" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">
@@ -39448,12 +39448,12 @@
       </c>
       <c r="AM318" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN318" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -39565,12 +39565,12 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN319" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO319" t="inlineStr">
@@ -39682,12 +39682,12 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN320" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO320" t="inlineStr">
@@ -39799,12 +39799,12 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN321" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO321" t="inlineStr">
@@ -39916,12 +39916,12 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN322" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO322" t="inlineStr">
@@ -40033,12 +40033,12 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN323" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO323" t="inlineStr">
@@ -40150,12 +40150,12 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN324" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO324" t="inlineStr">
@@ -40267,12 +40267,12 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN325" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO325" t="inlineStr">
